--- a/output/NL_291026_with_IDs.xlsx
+++ b/output/NL_291026_with_IDs.xlsx
@@ -2219,11 +2219,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>7202</v>
+        <v>7204</v>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>3PLDBSNL</t>
+          <t>3PLDBSBRNL</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
